--- a/backend/data/financials_by_company/04B.F.xlsx
+++ b/backend/data/financials_by_company/04B.F.xlsx
@@ -707,660 +707,660 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-27750</v>
+        <v>-484950</v>
       </c>
       <c r="C2" t="n">
-        <v>0.15</v>
+        <v>0.265</v>
       </c>
       <c r="D2" t="n">
-        <v>-11999000</v>
+        <v>3278000</v>
       </c>
       <c r="E2" t="n">
-        <v>-185000</v>
+        <v>-1830000</v>
       </c>
       <c r="F2" t="n">
-        <v>-185000</v>
+        <v>-1830000</v>
       </c>
       <c r="G2" t="n">
-        <v>-22006000</v>
+        <v>-796000</v>
       </c>
       <c r="H2" t="n">
-        <v>6062000</v>
+        <v>5366000</v>
       </c>
       <c r="I2" t="n">
-        <v>135376000</v>
+        <v>121607000</v>
       </c>
       <c r="J2" t="n">
-        <v>-12184000</v>
+        <v>1448000</v>
       </c>
       <c r="K2" t="n">
-        <v>-18246000</v>
+        <v>-3918000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2563000</v>
+        <v>-698000</v>
       </c>
       <c r="M2" t="n">
-        <v>2530000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>698000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>71000</v>
+      </c>
       <c r="O2" t="n">
-        <v>-21848750</v>
+        <v>549050</v>
       </c>
       <c r="P2" t="n">
-        <v>-22006000</v>
+        <v>-796000</v>
       </c>
       <c r="Q2" t="n">
-        <v>154262000</v>
+        <v>131060000</v>
       </c>
       <c r="R2" t="n">
-        <v>-5105000</v>
+        <v>-1780000</v>
       </c>
       <c r="S2" t="n">
-        <v>21442626</v>
+        <v>16464935</v>
       </c>
       <c r="T2" t="n">
-        <v>21442626</v>
+        <v>16300003</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.03</v>
+        <v>-0.05</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.03</v>
+        <v>-0.05</v>
       </c>
       <c r="W2" t="n">
-        <v>-22006000</v>
+        <v>-796000</v>
       </c>
       <c r="X2" t="n">
-        <v>-22006000</v>
+        <v>-796000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-22006000</v>
+        <v>-796000</v>
       </c>
       <c r="Z2" t="n">
-        <v>143000</v>
+        <v>-154000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-22149000</v>
+        <v>-642000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-22149000</v>
+        <v>-642000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1373000</v>
+        <v>-3974000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-20776000</v>
+        <v>-4616000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-8973000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-1327000</v>
-      </c>
+        <v>-1830000</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-501000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>-1830000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>-257000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>501000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>-7461000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>316000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2087000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-2563000</v>
+        <v>-698000</v>
       </c>
       <c r="AP2" t="n">
-        <v>33000</v>
+        <v>71000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2530000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>698000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>71000</v>
+      </c>
       <c r="AS2" t="n">
-        <v>-9240000</v>
+        <v>-2088000</v>
       </c>
       <c r="AT2" t="n">
-        <v>18886000</v>
+        <v>9453000</v>
       </c>
       <c r="AU2" t="n">
-        <v>291000</v>
+        <v>272000</v>
       </c>
       <c r="AV2" t="n">
-        <v>6062000</v>
+        <v>5366000</v>
       </c>
       <c r="AW2" t="n">
-        <v>6062000</v>
+        <v>5366000</v>
       </c>
       <c r="AX2" t="n">
-        <v>12533000</v>
+        <v>3815000</v>
       </c>
       <c r="AY2" t="n">
-        <v>12533000</v>
+        <v>3815000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3865000</v>
+        <v>1868000</v>
       </c>
       <c r="BA2" t="n">
-        <v>8668000</v>
+        <v>1947000</v>
       </c>
       <c r="BB2" t="n">
-        <v>9646000</v>
+        <v>7365000</v>
       </c>
       <c r="BC2" t="n">
-        <v>135376000</v>
+        <v>121607000</v>
       </c>
       <c r="BD2" t="n">
-        <v>145022000</v>
+        <v>128972000</v>
       </c>
       <c r="BE2" t="n">
-        <v>145022000</v>
+        <v>128972000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>4088800</v>
+        <v>-127770.934055</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4</v>
+        <v>0.094856</v>
       </c>
       <c r="D3" t="n">
-        <v>633000</v>
+        <v>-2633000</v>
       </c>
       <c r="E3" t="n">
-        <v>10222000</v>
+        <v>-1347000</v>
       </c>
       <c r="F3" t="n">
-        <v>10222000</v>
+        <v>-1347000</v>
       </c>
       <c r="G3" t="n">
-        <v>1323000</v>
+        <v>-9340000</v>
       </c>
       <c r="H3" t="n">
-        <v>5090000</v>
+        <v>5458000</v>
       </c>
       <c r="I3" t="n">
-        <v>153512000</v>
+        <v>208337000</v>
       </c>
       <c r="J3" t="n">
-        <v>10855000</v>
+        <v>-3980000</v>
       </c>
       <c r="K3" t="n">
-        <v>5765000</v>
+        <v>-9438000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2201000</v>
+        <v>-1015000</v>
       </c>
       <c r="M3" t="n">
-        <v>2057000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>904000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>-4810200</v>
+        <v>-8120770.934055</v>
       </c>
       <c r="P3" t="n">
-        <v>1323000</v>
+        <v>-9340000</v>
       </c>
       <c r="Q3" t="n">
-        <v>171436000</v>
+        <v>221718000</v>
       </c>
       <c r="R3" t="n">
-        <v>-4732000</v>
+        <v>-5463000</v>
       </c>
       <c r="S3" t="n">
-        <v>21494970</v>
+        <v>20410610</v>
       </c>
       <c r="T3" t="n">
-        <v>20818088</v>
+        <v>20300005</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06</v>
+        <v>-0.46</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06</v>
+        <v>-0.46</v>
       </c>
       <c r="W3" t="n">
-        <v>1323000</v>
+        <v>-9340000</v>
       </c>
       <c r="X3" t="n">
-        <v>1323000</v>
+        <v>-9340000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1323000</v>
+        <v>-9340000</v>
       </c>
       <c r="Z3" t="n">
-        <v>30000</v>
+        <v>21000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1293000</v>
+        <v>-9361000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1293000</v>
+        <v>-9361000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2415000</v>
+        <v>-981000</v>
       </c>
       <c r="AD3" t="n">
-        <v>3708000</v>
+        <v>-10342000</v>
       </c>
       <c r="AE3" t="n">
-        <v>16183000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>6745000</v>
-      </c>
+        <v>-1347000</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>10142000</v>
+        <v>-3001000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>10142000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>3001000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
       <c r="AM3" t="n">
-        <v>-784000</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>80000</v>
+        <v>1654000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2201000</v>
+        <v>-1015000</v>
       </c>
       <c r="AP3" t="n">
-        <v>144000</v>
+        <v>111000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2057000</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>904000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
       <c r="AS3" t="n">
-        <v>-10274000</v>
+        <v>-7980000</v>
       </c>
       <c r="AT3" t="n">
-        <v>17924000</v>
+        <v>13381000</v>
       </c>
       <c r="AU3" t="n">
-        <v>284000</v>
+        <v>71000</v>
       </c>
       <c r="AV3" t="n">
-        <v>5090000</v>
+        <v>5458000</v>
       </c>
       <c r="AW3" t="n">
-        <v>5090000</v>
+        <v>5458000</v>
       </c>
       <c r="AX3" t="n">
-        <v>12550000</v>
+        <v>7852000</v>
       </c>
       <c r="AY3" t="n">
-        <v>12550000</v>
+        <v>7852000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4668000</v>
+        <v>3655000</v>
       </c>
       <c r="BA3" t="n">
-        <v>7882000</v>
+        <v>4197000</v>
       </c>
       <c r="BB3" t="n">
-        <v>7650000</v>
+        <v>5401000</v>
       </c>
       <c r="BC3" t="n">
-        <v>153512000</v>
+        <v>208337000</v>
       </c>
       <c r="BD3" t="n">
-        <v>161162000</v>
+        <v>213738000</v>
       </c>
       <c r="BE3" t="n">
-        <v>161162000</v>
+        <v>213738000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-127770.934055</v>
+        <v>4088800</v>
       </c>
       <c r="C4" t="n">
-        <v>0.094856</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>-2633000</v>
+        <v>633000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1347000</v>
+        <v>10222000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1347000</v>
+        <v>10222000</v>
       </c>
       <c r="G4" t="n">
-        <v>-9340000</v>
+        <v>1323000</v>
       </c>
       <c r="H4" t="n">
-        <v>5458000</v>
+        <v>5090000</v>
       </c>
       <c r="I4" t="n">
-        <v>208337000</v>
+        <v>153512000</v>
       </c>
       <c r="J4" t="n">
-        <v>-3980000</v>
+        <v>10855000</v>
       </c>
       <c r="K4" t="n">
-        <v>-9438000</v>
+        <v>5765000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1015000</v>
+        <v>-2201000</v>
       </c>
       <c r="M4" t="n">
-        <v>904000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>2057000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-8120770.934055</v>
+        <v>-4810200</v>
       </c>
       <c r="P4" t="n">
-        <v>-9340000</v>
+        <v>1323000</v>
       </c>
       <c r="Q4" t="n">
-        <v>221718000</v>
+        <v>171436000</v>
       </c>
       <c r="R4" t="n">
-        <v>-5463000</v>
+        <v>-4732000</v>
       </c>
       <c r="S4" t="n">
-        <v>20410610</v>
+        <v>21494970</v>
       </c>
       <c r="T4" t="n">
-        <v>20300005</v>
+        <v>20818088</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.46</v>
+        <v>0.06</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.46</v>
+        <v>0.06</v>
       </c>
       <c r="W4" t="n">
-        <v>-9340000</v>
+        <v>1323000</v>
       </c>
       <c r="X4" t="n">
-        <v>-9340000</v>
+        <v>1323000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-9340000</v>
+        <v>1323000</v>
       </c>
       <c r="Z4" t="n">
-        <v>21000</v>
+        <v>30000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-9361000</v>
+        <v>1293000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-9361000</v>
+        <v>1293000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-981000</v>
+        <v>2415000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-10342000</v>
+        <v>3708000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1347000</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>16183000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>6745000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>-3001000</v>
+        <v>10142000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>10142000</v>
       </c>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>3001000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-784000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1654000</v>
+        <v>80000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1015000</v>
+        <v>-2201000</v>
       </c>
       <c r="AP4" t="n">
-        <v>111000</v>
+        <v>144000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>904000</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
+        <v>2057000</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>-7980000</v>
+        <v>-10274000</v>
       </c>
       <c r="AT4" t="n">
-        <v>13381000</v>
+        <v>17924000</v>
       </c>
       <c r="AU4" t="n">
-        <v>71000</v>
+        <v>284000</v>
       </c>
       <c r="AV4" t="n">
-        <v>5458000</v>
+        <v>5090000</v>
       </c>
       <c r="AW4" t="n">
-        <v>5458000</v>
+        <v>5090000</v>
       </c>
       <c r="AX4" t="n">
-        <v>7852000</v>
+        <v>12550000</v>
       </c>
       <c r="AY4" t="n">
-        <v>7852000</v>
+        <v>12550000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3655000</v>
+        <v>4668000</v>
       </c>
       <c r="BA4" t="n">
-        <v>4197000</v>
+        <v>7882000</v>
       </c>
       <c r="BB4" t="n">
-        <v>5401000</v>
+        <v>7650000</v>
       </c>
       <c r="BC4" t="n">
-        <v>208337000</v>
+        <v>153512000</v>
       </c>
       <c r="BD4" t="n">
-        <v>213738000</v>
+        <v>161162000</v>
       </c>
       <c r="BE4" t="n">
-        <v>213738000</v>
+        <v>161162000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-484950</v>
+        <v>-27750</v>
       </c>
       <c r="C5" t="n">
-        <v>0.265</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>3278000</v>
+        <v>-11999000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1830000</v>
+        <v>-185000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1830000</v>
+        <v>-185000</v>
       </c>
       <c r="G5" t="n">
-        <v>-796000</v>
+        <v>-22006000</v>
       </c>
       <c r="H5" t="n">
-        <v>5366000</v>
+        <v>6062000</v>
       </c>
       <c r="I5" t="n">
-        <v>121607000</v>
+        <v>135376000</v>
       </c>
       <c r="J5" t="n">
-        <v>1448000</v>
+        <v>-12184000</v>
       </c>
       <c r="K5" t="n">
-        <v>-3918000</v>
+        <v>-18246000</v>
       </c>
       <c r="L5" t="n">
-        <v>-698000</v>
+        <v>-2563000</v>
       </c>
       <c r="M5" t="n">
-        <v>698000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>71000</v>
-      </c>
+        <v>2530000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>549050</v>
+        <v>-21848750</v>
       </c>
       <c r="P5" t="n">
-        <v>-796000</v>
+        <v>-22006000</v>
       </c>
       <c r="Q5" t="n">
-        <v>131060000</v>
+        <v>154262000</v>
       </c>
       <c r="R5" t="n">
-        <v>-1780000</v>
+        <v>-5105000</v>
       </c>
       <c r="S5" t="n">
-        <v>16464935</v>
+        <v>21442626</v>
       </c>
       <c r="T5" t="n">
-        <v>16300003</v>
+        <v>21442626</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05</v>
+        <v>-1.03</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.05</v>
+        <v>-1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>-796000</v>
+        <v>-22006000</v>
       </c>
       <c r="X5" t="n">
-        <v>-796000</v>
+        <v>-22006000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-796000</v>
+        <v>-22006000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-154000</v>
+        <v>143000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-642000</v>
+        <v>-22149000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-642000</v>
+        <v>-22149000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3974000</v>
+        <v>1373000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-4616000</v>
+        <v>-20776000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1830000</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>-8973000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-1327000</v>
+      </c>
       <c r="AG5" t="n">
-        <v>-1830000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>-257000</v>
-      </c>
+        <v>-501000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2087000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>501000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>-7461000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>316000</v>
+      </c>
       <c r="AO5" t="n">
-        <v>-698000</v>
+        <v>-2563000</v>
       </c>
       <c r="AP5" t="n">
-        <v>71000</v>
+        <v>33000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>698000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>71000</v>
-      </c>
+        <v>2530000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>-2088000</v>
+        <v>-9240000</v>
       </c>
       <c r="AT5" t="n">
-        <v>9453000</v>
+        <v>18886000</v>
       </c>
       <c r="AU5" t="n">
-        <v>272000</v>
+        <v>291000</v>
       </c>
       <c r="AV5" t="n">
-        <v>5366000</v>
+        <v>6062000</v>
       </c>
       <c r="AW5" t="n">
-        <v>5366000</v>
+        <v>6062000</v>
       </c>
       <c r="AX5" t="n">
-        <v>3815000</v>
+        <v>12533000</v>
       </c>
       <c r="AY5" t="n">
-        <v>3815000</v>
+        <v>12533000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1868000</v>
+        <v>3865000</v>
       </c>
       <c r="BA5" t="n">
-        <v>1947000</v>
+        <v>8668000</v>
       </c>
       <c r="BB5" t="n">
-        <v>7365000</v>
+        <v>9646000</v>
       </c>
       <c r="BC5" t="n">
-        <v>121607000</v>
+        <v>135376000</v>
       </c>
       <c r="BD5" t="n">
-        <v>128972000</v>
+        <v>145022000</v>
       </c>
       <c r="BE5" t="n">
-        <v>128972000</v>
+        <v>145022000</v>
       </c>
     </row>
   </sheetData>
@@ -1711,776 +1711,776 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1038260</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>20519342</v>
+        <v>20300005</v>
       </c>
       <c r="D2" t="n">
-        <v>21557602</v>
-      </c>
-      <c r="E2" t="n">
-        <v>27000000</v>
-      </c>
+        <v>20300005</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>28577000</v>
+        <v>368000</v>
       </c>
       <c r="G2" t="n">
-        <v>83643000</v>
+        <v>110162000</v>
       </c>
       <c r="H2" t="n">
-        <v>113597000</v>
+        <v>115312000</v>
       </c>
       <c r="I2" t="n">
-        <v>-33686000</v>
+        <v>2308000</v>
       </c>
       <c r="J2" t="n">
-        <v>83643000</v>
+        <v>110162000</v>
       </c>
       <c r="K2" t="n">
-        <v>85020000</v>
+        <v>114944000</v>
       </c>
       <c r="L2" t="n">
-        <v>85466000</v>
+        <v>115080000</v>
       </c>
       <c r="M2" t="n">
-        <v>98566000</v>
+        <v>127739000</v>
       </c>
       <c r="N2" t="n">
-        <v>13546000</v>
+        <v>12795000</v>
       </c>
       <c r="O2" t="n">
-        <v>85020000</v>
+        <v>114944000</v>
       </c>
       <c r="P2" t="n">
-        <v>1961000</v>
+        <v>293000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1961000</v>
+        <v>293000</v>
       </c>
       <c r="R2" t="n">
-        <v>-43486000</v>
+        <v>1759000</v>
       </c>
       <c r="S2" t="n">
-        <v>7137000</v>
+        <v>36000</v>
       </c>
       <c r="T2" t="n">
-        <v>119408000</v>
+        <v>112856000</v>
       </c>
       <c r="U2" t="n">
-        <v>119408000</v>
+        <v>112856000</v>
       </c>
       <c r="V2" t="n">
-        <v>72240000</v>
+        <v>48331000</v>
       </c>
       <c r="W2" t="n">
-        <v>16015000</v>
+        <v>27079000</v>
       </c>
       <c r="X2" t="n">
-        <v>2123000</v>
+        <v>9288000</v>
       </c>
       <c r="Y2" t="n">
-        <v>4878000</v>
+        <v>3368000</v>
       </c>
       <c r="Z2" t="n">
-        <v>4878000</v>
+        <v>3368000</v>
       </c>
       <c r="AA2" t="n">
-        <v>446000</v>
+        <v>136000</v>
       </c>
       <c r="AB2" t="n">
-        <v>446000</v>
+        <v>136000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8568000</v>
+        <v>14287000</v>
       </c>
       <c r="AD2" t="n">
-        <v>56225000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>12481000</v>
-      </c>
+        <v>21252000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>28131000</v>
+        <v>232000</v>
       </c>
       <c r="AG2" t="n">
-        <v>28131000</v>
+        <v>232000</v>
       </c>
       <c r="AH2" t="n">
-        <v>15613000</v>
+        <v>21020000</v>
       </c>
       <c r="AI2" t="n">
-        <v>170806000</v>
+        <v>176070000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>148267000</v>
+        <v>152510000</v>
       </c>
       <c r="AK2" t="n">
-        <v>546000</v>
+        <v>1130000</v>
       </c>
       <c r="AL2" t="n">
-        <v>546000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>1130000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="n">
-        <v>7835000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>2803000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2803000</v>
+      </c>
       <c r="AP2" t="n">
-        <v>2616000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2616000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>5219000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5219000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>1377000</v>
+        <v>4782000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1377000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>1781000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3001000</v>
+      </c>
       <c r="AX2" t="n">
-        <v>138509000</v>
+        <v>143795000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-28485000</v>
+        <v>-12052000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>166994000</v>
+        <v>155847000</v>
       </c>
       <c r="BA2" t="n">
-        <v>86362000</v>
+        <v>72609000</v>
       </c>
       <c r="BB2" t="n">
-        <v>80632000</v>
+        <v>83238000</v>
       </c>
       <c r="BC2" t="n">
-        <v>22539000</v>
-      </c>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="n">
-        <v>2401000</v>
-      </c>
+        <v>23560000</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>1108000</v>
+        <v>778000</v>
       </c>
       <c r="BG2" t="n">
-        <v>979000</v>
+        <v>1038000</v>
       </c>
       <c r="BH2" t="n">
-        <v>16474000</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
+        <v>17246000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
       <c r="BJ2" t="n">
-        <v>429000</v>
+        <v>13094000</v>
       </c>
       <c r="BK2" t="n">
-        <v>314000</v>
+        <v>711000</v>
       </c>
       <c r="BL2" t="n">
-        <v>15731000</v>
+        <v>3441000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1577000</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+        <v>4498000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
       <c r="BO2" t="n">
-        <v>1577000</v>
+        <v>4498000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>807961</v>
+        <v>876485</v>
       </c>
       <c r="C3" t="n">
-        <v>20592057</v>
+        <v>19423520</v>
       </c>
       <c r="D3" t="n">
-        <v>21400018</v>
+        <v>20300005</v>
       </c>
       <c r="E3" t="n">
-        <v>27599000</v>
+        <v>63713000</v>
       </c>
       <c r="F3" t="n">
-        <v>29214000</v>
+        <v>66405000</v>
       </c>
       <c r="G3" t="n">
-        <v>101721000</v>
+        <v>102172000</v>
       </c>
       <c r="H3" t="n">
-        <v>132396000</v>
+        <v>170272000</v>
       </c>
       <c r="I3" t="n">
-        <v>-7007000</v>
+        <v>-4114000</v>
       </c>
       <c r="J3" t="n">
-        <v>101721000</v>
+        <v>102172000</v>
       </c>
       <c r="K3" t="n">
-        <v>103182000</v>
+        <v>103867000</v>
       </c>
       <c r="L3" t="n">
-        <v>132127000</v>
+        <v>169924000</v>
       </c>
       <c r="M3" t="n">
-        <v>116871000</v>
+        <v>117670000</v>
       </c>
       <c r="N3" t="n">
-        <v>13689000</v>
+        <v>13803000</v>
       </c>
       <c r="O3" t="n">
-        <v>103182000</v>
+        <v>103867000</v>
       </c>
       <c r="P3" t="n">
-        <v>389000</v>
+        <v>2096000</v>
       </c>
       <c r="Q3" t="n">
-        <v>389000</v>
+        <v>2096000</v>
       </c>
       <c r="R3" t="n">
-        <v>-21480000</v>
+        <v>-7581000</v>
       </c>
       <c r="S3" t="n">
-        <v>6062000</v>
+        <v>1903000</v>
       </c>
       <c r="T3" t="n">
-        <v>118211000</v>
+        <v>107449000</v>
       </c>
       <c r="U3" t="n">
-        <v>118211000</v>
+        <v>107449000</v>
       </c>
       <c r="V3" t="n">
-        <v>71641000</v>
+        <v>109307000</v>
       </c>
       <c r="W3" t="n">
-        <v>43575000</v>
+        <v>79451000</v>
       </c>
       <c r="X3" t="n">
-        <v>2001000</v>
+        <v>1893000</v>
       </c>
       <c r="Y3" t="n">
-        <v>3761000</v>
+        <v>3341000</v>
       </c>
       <c r="Z3" t="n">
-        <v>3761000</v>
+        <v>3341000</v>
       </c>
       <c r="AA3" t="n">
-        <v>28945000</v>
+        <v>66057000</v>
       </c>
       <c r="AB3" t="n">
-        <v>28945000</v>
+        <v>66057000</v>
       </c>
       <c r="AC3" t="n">
-        <v>8868000</v>
+        <v>8160000</v>
       </c>
       <c r="AD3" t="n">
-        <v>28066000</v>
+        <v>29856000</v>
       </c>
       <c r="AE3" t="n">
-        <v>8583000</v>
+        <v>8477000</v>
       </c>
       <c r="AF3" t="n">
-        <v>269000</v>
+        <v>348000</v>
       </c>
       <c r="AG3" t="n">
-        <v>269000</v>
+        <v>348000</v>
       </c>
       <c r="AH3" t="n">
-        <v>19214000</v>
+        <v>21031000</v>
       </c>
       <c r="AI3" t="n">
-        <v>188512000</v>
+        <v>226977000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>167453000</v>
+        <v>201235000</v>
       </c>
       <c r="AK3" t="n">
-        <v>446000</v>
+        <v>2141000</v>
       </c>
       <c r="AL3" t="n">
-        <v>446000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>2141000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>329000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>28891000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
+        <v>3132000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2803000</v>
+      </c>
       <c r="AP3" t="n">
-        <v>2709000</v>
+        <v>3132000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2709000</v>
+        <v>2803000</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>329000</v>
       </c>
       <c r="AS3" t="n">
-        <v>26182000</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>26182000</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>1461000</v>
+        <v>1695000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1461000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>1695000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
       <c r="AX3" t="n">
-        <v>136655000</v>
+        <v>194267000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-22210000</v>
+        <v>-17312000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>158865000</v>
+        <v>211579000</v>
       </c>
       <c r="BA3" t="n">
-        <v>78817000</v>
+        <v>132828000</v>
       </c>
       <c r="BB3" t="n">
-        <v>80048000</v>
+        <v>78751000</v>
       </c>
       <c r="BC3" t="n">
-        <v>21059000</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
+        <v>25742000</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>429000</v>
+      </c>
       <c r="BE3" t="n">
-        <v>3173000</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1440000</v>
+        <v>2171000</v>
       </c>
       <c r="BG3" t="n">
-        <v>857000</v>
+        <v>2065000</v>
       </c>
       <c r="BH3" t="n">
-        <v>13974000</v>
-      </c>
-      <c r="BI3" t="inlineStr"/>
+        <v>18385000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
       <c r="BJ3" t="n">
-        <v>764000</v>
+        <v>500000</v>
       </c>
       <c r="BK3" t="n">
-        <v>314000</v>
+        <v>952000</v>
       </c>
       <c r="BL3" t="n">
-        <v>12896000</v>
+        <v>16933000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1615000</v>
+        <v>3121000</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>429000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1615000</v>
+        <v>2692000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>876485</v>
+        <v>807961</v>
       </c>
       <c r="C4" t="n">
-        <v>19423520</v>
+        <v>20592057</v>
       </c>
       <c r="D4" t="n">
-        <v>20300005</v>
+        <v>21400018</v>
       </c>
       <c r="E4" t="n">
-        <v>63713000</v>
+        <v>27599000</v>
       </c>
       <c r="F4" t="n">
-        <v>66405000</v>
+        <v>29214000</v>
       </c>
       <c r="G4" t="n">
-        <v>102172000</v>
+        <v>101721000</v>
       </c>
       <c r="H4" t="n">
-        <v>170272000</v>
+        <v>132396000</v>
       </c>
       <c r="I4" t="n">
-        <v>-4114000</v>
+        <v>-7007000</v>
       </c>
       <c r="J4" t="n">
-        <v>102172000</v>
+        <v>101721000</v>
       </c>
       <c r="K4" t="n">
-        <v>103867000</v>
+        <v>103182000</v>
       </c>
       <c r="L4" t="n">
-        <v>169924000</v>
+        <v>132127000</v>
       </c>
       <c r="M4" t="n">
-        <v>117670000</v>
+        <v>116871000</v>
       </c>
       <c r="N4" t="n">
-        <v>13803000</v>
+        <v>13689000</v>
       </c>
       <c r="O4" t="n">
-        <v>103867000</v>
+        <v>103182000</v>
       </c>
       <c r="P4" t="n">
-        <v>2096000</v>
+        <v>389000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2096000</v>
+        <v>389000</v>
       </c>
       <c r="R4" t="n">
-        <v>-7581000</v>
+        <v>-21480000</v>
       </c>
       <c r="S4" t="n">
-        <v>1903000</v>
+        <v>6062000</v>
       </c>
       <c r="T4" t="n">
-        <v>107449000</v>
+        <v>118211000</v>
       </c>
       <c r="U4" t="n">
-        <v>107449000</v>
+        <v>118211000</v>
       </c>
       <c r="V4" t="n">
-        <v>109307000</v>
+        <v>71641000</v>
       </c>
       <c r="W4" t="n">
-        <v>79451000</v>
+        <v>43575000</v>
       </c>
       <c r="X4" t="n">
-        <v>1893000</v>
+        <v>2001000</v>
       </c>
       <c r="Y4" t="n">
-        <v>3341000</v>
+        <v>3761000</v>
       </c>
       <c r="Z4" t="n">
-        <v>3341000</v>
+        <v>3761000</v>
       </c>
       <c r="AA4" t="n">
-        <v>66057000</v>
+        <v>28945000</v>
       </c>
       <c r="AB4" t="n">
-        <v>66057000</v>
+        <v>28945000</v>
       </c>
       <c r="AC4" t="n">
-        <v>8160000</v>
+        <v>8868000</v>
       </c>
       <c r="AD4" t="n">
-        <v>29856000</v>
+        <v>28066000</v>
       </c>
       <c r="AE4" t="n">
-        <v>8477000</v>
+        <v>8583000</v>
       </c>
       <c r="AF4" t="n">
-        <v>348000</v>
+        <v>269000</v>
       </c>
       <c r="AG4" t="n">
-        <v>348000</v>
+        <v>269000</v>
       </c>
       <c r="AH4" t="n">
-        <v>21031000</v>
+        <v>19214000</v>
       </c>
       <c r="AI4" t="n">
-        <v>226977000</v>
+        <v>188512000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>201235000</v>
+        <v>167453000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2141000</v>
+        <v>446000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2141000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>329000</v>
-      </c>
+        <v>446000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>3132000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2803000</v>
-      </c>
+        <v>28891000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>3132000</v>
+        <v>2709000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2803000</v>
+        <v>2709000</v>
       </c>
       <c r="AR4" t="n">
-        <v>329000</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>26182000</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>26182000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1695000</v>
+        <v>1461000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1695000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
+        <v>1461000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>194267000</v>
+        <v>136655000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-17312000</v>
+        <v>-22210000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>211579000</v>
+        <v>158865000</v>
       </c>
       <c r="BA4" t="n">
-        <v>132828000</v>
+        <v>78817000</v>
       </c>
       <c r="BB4" t="n">
-        <v>78751000</v>
+        <v>80048000</v>
       </c>
       <c r="BC4" t="n">
-        <v>25742000</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>429000</v>
-      </c>
+        <v>21059000</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>3173000</v>
       </c>
       <c r="BF4" t="n">
-        <v>2171000</v>
+        <v>1440000</v>
       </c>
       <c r="BG4" t="n">
-        <v>2065000</v>
+        <v>857000</v>
       </c>
       <c r="BH4" t="n">
-        <v>18385000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
+        <v>13974000</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>500000</v>
+        <v>764000</v>
       </c>
       <c r="BK4" t="n">
-        <v>952000</v>
+        <v>314000</v>
       </c>
       <c r="BL4" t="n">
-        <v>16933000</v>
+        <v>12896000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3121000</v>
+        <v>1615000</v>
       </c>
       <c r="BN4" t="n">
-        <v>429000</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>2692000</v>
+        <v>1615000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1038260</v>
+      </c>
       <c r="C5" t="n">
-        <v>20300005</v>
+        <v>20519342</v>
       </c>
       <c r="D5" t="n">
-        <v>20300005</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>21557602</v>
+      </c>
+      <c r="E5" t="n">
+        <v>27000000</v>
+      </c>
       <c r="F5" t="n">
-        <v>368000</v>
+        <v>28577000</v>
       </c>
       <c r="G5" t="n">
-        <v>110162000</v>
+        <v>83643000</v>
       </c>
       <c r="H5" t="n">
-        <v>115312000</v>
+        <v>113597000</v>
       </c>
       <c r="I5" t="n">
-        <v>2308000</v>
+        <v>-33686000</v>
       </c>
       <c r="J5" t="n">
-        <v>110162000</v>
+        <v>83643000</v>
       </c>
       <c r="K5" t="n">
-        <v>114944000</v>
+        <v>85020000</v>
       </c>
       <c r="L5" t="n">
-        <v>115080000</v>
+        <v>85466000</v>
       </c>
       <c r="M5" t="n">
-        <v>127739000</v>
+        <v>98566000</v>
       </c>
       <c r="N5" t="n">
-        <v>12795000</v>
+        <v>13546000</v>
       </c>
       <c r="O5" t="n">
-        <v>114944000</v>
+        <v>85020000</v>
       </c>
       <c r="P5" t="n">
-        <v>293000</v>
+        <v>1961000</v>
       </c>
       <c r="Q5" t="n">
-        <v>293000</v>
+        <v>1961000</v>
       </c>
       <c r="R5" t="n">
-        <v>1759000</v>
+        <v>-43486000</v>
       </c>
       <c r="S5" t="n">
-        <v>36000</v>
+        <v>7137000</v>
       </c>
       <c r="T5" t="n">
-        <v>112856000</v>
+        <v>119408000</v>
       </c>
       <c r="U5" t="n">
-        <v>112856000</v>
+        <v>119408000</v>
       </c>
       <c r="V5" t="n">
-        <v>48331000</v>
+        <v>72240000</v>
       </c>
       <c r="W5" t="n">
-        <v>27079000</v>
+        <v>16015000</v>
       </c>
       <c r="X5" t="n">
-        <v>9288000</v>
+        <v>2123000</v>
       </c>
       <c r="Y5" t="n">
-        <v>3368000</v>
+        <v>4878000</v>
       </c>
       <c r="Z5" t="n">
-        <v>3368000</v>
+        <v>4878000</v>
       </c>
       <c r="AA5" t="n">
-        <v>136000</v>
+        <v>446000</v>
       </c>
       <c r="AB5" t="n">
-        <v>136000</v>
+        <v>446000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14287000</v>
+        <v>8568000</v>
       </c>
       <c r="AD5" t="n">
-        <v>21252000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>56225000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>12481000</v>
+      </c>
       <c r="AF5" t="n">
-        <v>232000</v>
+        <v>28131000</v>
       </c>
       <c r="AG5" t="n">
-        <v>232000</v>
+        <v>28131000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21020000</v>
+        <v>15613000</v>
       </c>
       <c r="AI5" t="n">
-        <v>176070000</v>
+        <v>170806000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>152510000</v>
+        <v>148267000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1130000</v>
+        <v>546000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1130000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>546000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>2803000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>2803000</v>
-      </c>
+        <v>7835000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+        <v>2616000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2616000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>5219000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5219000</v>
+      </c>
       <c r="AU5" t="n">
-        <v>4782000</v>
+        <v>1377000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1781000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3001000</v>
-      </c>
+        <v>1377000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>143795000</v>
+        <v>138509000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-12052000</v>
+        <v>-28485000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>155847000</v>
+        <v>166994000</v>
       </c>
       <c r="BA5" t="n">
-        <v>72609000</v>
+        <v>86362000</v>
       </c>
       <c r="BB5" t="n">
-        <v>83238000</v>
+        <v>80632000</v>
       </c>
       <c r="BC5" t="n">
-        <v>23560000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
+        <v>22539000</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>2401000</v>
+      </c>
       <c r="BF5" t="n">
-        <v>778000</v>
+        <v>1108000</v>
       </c>
       <c r="BG5" t="n">
-        <v>1038000</v>
+        <v>979000</v>
       </c>
       <c r="BH5" t="n">
-        <v>17246000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
+        <v>16474000</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>13094000</v>
+        <v>429000</v>
       </c>
       <c r="BK5" t="n">
-        <v>711000</v>
+        <v>314000</v>
       </c>
       <c r="BL5" t="n">
-        <v>3441000</v>
+        <v>15731000</v>
       </c>
       <c r="BM5" t="n">
-        <v>4498000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
+        <v>1577000</v>
+      </c>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="n">
-        <v>4498000</v>
+        <v>1577000</v>
       </c>
     </row>
   </sheetData>
@@ -2776,628 +2776,628 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-10478000</v>
+        <v>-37597000</v>
       </c>
       <c r="C2" t="n">
-        <v>-1290000</v>
+        <v>-1637000</v>
       </c>
       <c r="D2" t="n">
-        <v>-636000</v>
+        <v>-50000000</v>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-7868000</v>
+        <v>-37181000</v>
       </c>
       <c r="H2" t="n">
-        <v>1577000</v>
+        <v>4498000</v>
       </c>
       <c r="I2" t="n">
-        <v>1615000</v>
+        <v>2000</v>
       </c>
       <c r="J2" t="n">
-        <v>-74000</v>
+        <v>40000</v>
       </c>
       <c r="K2" t="n">
-        <v>36000</v>
+        <v>4456000</v>
       </c>
       <c r="L2" t="n">
-        <v>-911000</v>
+        <v>41606000</v>
       </c>
       <c r="M2" t="n">
-        <v>-911000</v>
+        <v>41606000</v>
       </c>
       <c r="N2" t="n">
-        <v>-282000</v>
+        <v>94530000</v>
       </c>
       <c r="O2" t="n">
-        <v>-2153000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3450000</v>
-      </c>
+        <v>-698000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-1290000</v>
+        <v>-1637000</v>
       </c>
       <c r="S2" t="n">
-        <v>-1290000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
+        <v>-1637000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>-636000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-50589000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-50000000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-50000000</v>
+      </c>
       <c r="X2" t="n">
-        <v>-636000</v>
+        <v>-589000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-636000</v>
+        <v>-50589000</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>3557000</v>
+        <v>-36734000</v>
       </c>
       <c r="AB2" t="n">
-        <v>3557000</v>
+        <v>-36734000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3233000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>17778000</v>
-      </c>
+        <v>3250000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-2803000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-3120000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-3120000</v>
-      </c>
+        <v>-2803000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-7868000</v>
+        <v>-37181000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-7868000</v>
+        <v>-37181000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-2610000</v>
+        <v>-416000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2610000</v>
+        <v>-416000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-3213000</v>
+        <v>-3377000</v>
       </c>
       <c r="AO2" t="n">
-        <v>4074000</v>
+        <v>2672000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3844000</v>
+        <v>36000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>501000</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1252000</v>
+        <v>-4214000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1252000</v>
+        <v>-4214000</v>
       </c>
       <c r="AT2" t="n">
-        <v>6062000</v>
+        <v>5366000</v>
       </c>
       <c r="AU2" t="n">
-        <v>6062000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-191000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-191000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-5774000</v>
-      </c>
+        <v>5366000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>7019000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7461000</v>
-      </c>
+        <v>-257000</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>-442000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-22149000</v>
+        <v>-642000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-15747000</v>
+        <v>-55446000</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>-5986000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="n">
-        <v>967000</v>
+        <v>61462000</v>
       </c>
       <c r="F3" t="n">
-        <v>9770000</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-23966000</v>
+        <v>-52927000</v>
       </c>
       <c r="H3" t="n">
-        <v>1615000</v>
+        <v>2692000</v>
       </c>
       <c r="I3" t="n">
-        <v>2692000</v>
+        <v>4498000</v>
       </c>
       <c r="J3" t="n">
-        <v>113000</v>
+        <v>466000</v>
       </c>
       <c r="K3" t="n">
-        <v>-1190000</v>
+        <v>-2272000</v>
       </c>
       <c r="L3" t="n">
-        <v>8363000</v>
+        <v>55808000</v>
       </c>
       <c r="M3" t="n">
-        <v>8363000</v>
+        <v>55808000</v>
       </c>
       <c r="N3" t="n">
-        <v>-298000</v>
+        <v>1029000</v>
       </c>
       <c r="O3" t="n">
-        <v>-2076000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
+        <v>-697000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>9770000</v>
+        <v>-5986000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-5986000</v>
       </c>
       <c r="T3" t="n">
-        <v>9770000</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>967000</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>61462000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" t="n">
-        <v>967000</v>
+        <v>61462000</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>967000</v>
+        <v>61462000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-17772000</v>
+        <v>-55561000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-17772000</v>
+        <v>-55561000</v>
       </c>
       <c r="AC3" t="n">
-        <v>45000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
+        <v>-2634000</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>6249000</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>21471000</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-15222000</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-23966000</v>
+        <v>-52927000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-23966000</v>
+        <v>-52927000</v>
       </c>
       <c r="AL3" t="n">
-        <v>8219000</v>
+        <v>-2519000</v>
       </c>
       <c r="AM3" t="n">
-        <v>8219000</v>
+        <v>-2519000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1315000</v>
+        <v>-2045000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2485000</v>
+        <v>734000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5258000</v>
+        <v>2446000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>3001000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2229000</v>
+        <v>-1100000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2229000</v>
+        <v>-1100000</v>
       </c>
       <c r="AT3" t="n">
-        <v>5090000</v>
+        <v>5458000</v>
       </c>
       <c r="AU3" t="n">
-        <v>5090000</v>
+        <v>5458000</v>
       </c>
       <c r="AV3" t="n">
-        <v>192000</v>
+        <v>198000</v>
       </c>
       <c r="AW3" t="n">
-        <v>192000</v>
+        <v>198000</v>
       </c>
       <c r="AX3" t="n">
-        <v>4898000</v>
+        <v>5260000</v>
       </c>
       <c r="AY3" t="n">
-        <v>-9451000</v>
+        <v>-1652000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>784000</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-555000</v>
+        <v>-774000</v>
       </c>
       <c r="BB3" t="n">
-        <v>462000</v>
+        <v>-878000</v>
       </c>
       <c r="BC3" t="n">
-        <v>-10142000</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>1293000</v>
+        <v>-9361000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-55446000</v>
+        <v>-15747000</v>
       </c>
       <c r="C4" t="n">
-        <v>-5986000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>61462000</v>
+        <v>967000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>9770000</v>
       </c>
       <c r="G4" t="n">
-        <v>-52927000</v>
+        <v>-23966000</v>
       </c>
       <c r="H4" t="n">
+        <v>1615000</v>
+      </c>
+      <c r="I4" t="n">
         <v>2692000</v>
       </c>
-      <c r="I4" t="n">
-        <v>4498000</v>
-      </c>
       <c r="J4" t="n">
-        <v>466000</v>
+        <v>113000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2272000</v>
+        <v>-1190000</v>
       </c>
       <c r="L4" t="n">
-        <v>55808000</v>
+        <v>8363000</v>
       </c>
       <c r="M4" t="n">
-        <v>55808000</v>
+        <v>8363000</v>
       </c>
       <c r="N4" t="n">
-        <v>1029000</v>
+        <v>-298000</v>
       </c>
       <c r="O4" t="n">
-        <v>-697000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>-2076000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-5986000</v>
+        <v>9770000</v>
       </c>
       <c r="S4" t="n">
-        <v>-5986000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>9770000</v>
       </c>
       <c r="U4" t="n">
-        <v>61462000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
+        <v>967000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>61462000</v>
+        <v>967000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>61462000</v>
+        <v>967000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-55561000</v>
+        <v>-17772000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-55561000</v>
+        <v>-17772000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2634000</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>45000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>6249000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>21471000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-15222000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-52927000</v>
+        <v>-23966000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-52927000</v>
+        <v>-23966000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-2519000</v>
+        <v>8219000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-2519000</v>
+        <v>8219000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-2045000</v>
+        <v>1315000</v>
       </c>
       <c r="AO4" t="n">
-        <v>734000</v>
+        <v>2485000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2446000</v>
+        <v>5258000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3001000</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-1100000</v>
+        <v>2229000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-1100000</v>
+        <v>2229000</v>
       </c>
       <c r="AT4" t="n">
-        <v>5458000</v>
+        <v>5090000</v>
       </c>
       <c r="AU4" t="n">
-        <v>5458000</v>
+        <v>5090000</v>
       </c>
       <c r="AV4" t="n">
-        <v>198000</v>
+        <v>192000</v>
       </c>
       <c r="AW4" t="n">
-        <v>198000</v>
+        <v>192000</v>
       </c>
       <c r="AX4" t="n">
-        <v>5260000</v>
+        <v>4898000</v>
       </c>
       <c r="AY4" t="n">
-        <v>-1652000</v>
+        <v>-9451000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>784000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-774000</v>
+        <v>-555000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-878000</v>
+        <v>462000</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>-10142000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-9361000</v>
+        <v>1293000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-37597000</v>
+        <v>-10478000</v>
       </c>
       <c r="C5" t="n">
-        <v>-1637000</v>
+        <v>-1290000</v>
       </c>
       <c r="D5" t="n">
-        <v>-50000000</v>
+        <v>-636000</v>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" t="n">
-        <v>-37181000</v>
+        <v>-7868000</v>
       </c>
       <c r="H5" t="n">
-        <v>4498000</v>
+        <v>1577000</v>
       </c>
       <c r="I5" t="n">
-        <v>2000</v>
+        <v>1615000</v>
       </c>
       <c r="J5" t="n">
-        <v>40000</v>
+        <v>-74000</v>
       </c>
       <c r="K5" t="n">
-        <v>4456000</v>
+        <v>36000</v>
       </c>
       <c r="L5" t="n">
-        <v>41606000</v>
+        <v>-911000</v>
       </c>
       <c r="M5" t="n">
-        <v>41606000</v>
+        <v>-911000</v>
       </c>
       <c r="N5" t="n">
-        <v>94530000</v>
+        <v>-282000</v>
       </c>
       <c r="O5" t="n">
-        <v>-698000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>-2153000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3450000</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-1637000</v>
+        <v>-1290000</v>
       </c>
       <c r="S5" t="n">
-        <v>-1637000</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>-1290000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
       <c r="U5" t="n">
-        <v>-50589000</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-50000000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-50000000</v>
-      </c>
+        <v>-636000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-589000</v>
+        <v>-636000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-50589000</v>
+        <v>-636000</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>-36734000</v>
+        <v>3557000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-36734000</v>
+        <v>3557000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>-3233000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17778000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-2803000</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2803000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-3120000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-3120000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>-37181000</v>
+        <v>-7868000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-37181000</v>
+        <v>-7868000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-416000</v>
+        <v>-2610000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-416000</v>
+        <v>-2610000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-3377000</v>
+        <v>-3213000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2672000</v>
+        <v>4074000</v>
       </c>
       <c r="AP5" t="n">
-        <v>36000</v>
+        <v>3844000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>501000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-4214000</v>
+        <v>1252000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-4214000</v>
+        <v>1252000</v>
       </c>
       <c r="AT5" t="n">
-        <v>5366000</v>
+        <v>6062000</v>
       </c>
       <c r="AU5" t="n">
-        <v>5366000</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
+        <v>6062000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-191000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-191000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-5774000</v>
+      </c>
       <c r="AY5" t="n">
-        <v>-257000</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
+        <v>7019000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>7461000</v>
+      </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
+        <v>-442000</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
       <c r="BD5" t="n">
-        <v>-642000</v>
+        <v>-22149000</v>
       </c>
     </row>
   </sheetData>
@@ -3897,197 +3897,197 @@
       </c>
       <c r="CS1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jesse  Douglas', 'age': 45, 'title': 'CEO &amp; Director', 'yearBorn': 1980, 'fiscalYear': 2024, 'totalPay': 388876, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nikolaus  Kiefer', 'title': 'Co-Founder, CFO, Chief Investment Officer &amp; Executive Advisor', 'fiscalYear': 2024, 'totalPay': 389584, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jesse  Douglas', 'age': 45, 'title': 'CEO &amp; Director', 'yearBorn': 1980, 'fiscalYear': 2024, 'totalPay': 384643, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Nikolaus  Kiefer', 'title': 'Co-Founder, CFO, Chief Investment Officer &amp; Executive Advisor', 'fiscalYear': 2024, 'totalPay': 385344, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.175</v>
+        <v>0.177</v>
       </c>
       <c r="AD2" t="n">
         <v>5149</v>
@@ -4247,7 +4247,7 @@
         <v>1.34</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="AO2" t="n">
         <v>6.9</v>
@@ -4262,7 +4262,7 @@
         <v>1.36</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.7005</v>
+        <v>1.6376</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -4294,16 +4294,16 @@
         <v>0.3076</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.32509</v>
+        <v>0.32667</v>
       </c>
       <c r="BD2" t="n">
         <v>20991297</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.1441054</v>
+        <v>2.12049</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.6342972</v>
+        <v>0.6413612</v>
       </c>
       <c r="BG2" t="n">
         <v>1735603200</v>
@@ -4327,10 +4327,10 @@
         <v>-17.441</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.5072464</v>
+        <v>-0.44262296</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4439,148 +4439,148 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
+          <t>Green Impact Partners Inc.</t>
+        </is>
+      </c>
+      <c r="CT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1623218400000</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>1.36 - 1.36</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.01999998</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.014925359</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>1.34 - 2.62</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>-1.2599999</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.480916</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-44.262295</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1782158400</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1782158400</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>1771398165</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>finmb_704622724</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
           <t>Green Impact Partners Inc.    R</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>Green Impact Partners Inc.</t>
-        </is>
-      </c>
-      <c r="CU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>1.36 - 1.36</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="CX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>0.01999998</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.014925359</v>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>1.34 - 2.76</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>-0.5072464</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>-50.724636</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>1780430400</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1780430400</v>
-      </c>
-      <c r="DG2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.3405</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.20023522</v>
-      </c>
-      <c r="DM2" t="n">
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.27759993</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.16951632</v>
+      </c>
+      <c r="EA2" t="n">
         <v>15</v>
       </c>
-      <c r="DN2" t="n">
+      <c r="EB2" t="n">
         <v>15</v>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Blackheath Resources Inc.</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1623218400000</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>finmb_704622724</t>
-        </is>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1771398165</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>POSTPOST</t>
-        </is>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="EE2" t="b">
+        <v>0</v>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
